--- a/data/kz/niches/niche_formats_LASH.xlsx
+++ b/data/kz/niches/niche_formats_LASH.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -641,12 +642,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -692,12 +693,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -768,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,12 +825,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -861,12 +863,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -899,12 +901,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -937,12 +939,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1007,6 +1009,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1057,12 +1060,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1094,12 +1097,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1162,6 +1165,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1261,6 +1265,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1575,6 +1580,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1719,6 +1725,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1804,7 +1811,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1858,12 +1865,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1917,12 +1924,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2022,6 +2029,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2155,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2217,12 +2225,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2292,12 +2300,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2403,6 +2411,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2478,7 +2487,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2520,12 +2529,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2563,12 +2572,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2642,6 +2651,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2717,7 +2727,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2757,12 +2767,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2802,12 +2812,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2880,6 +2890,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2940,7 +2951,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2977,12 +2988,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3019,12 +3030,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3097,6 +3108,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3172,7 +3184,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3228,12 +3240,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_RENT</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3289,12 +3301,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3381,6 +3393,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3431,7 +3444,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3465,7 +3478,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3499,7 +3512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3533,7 +3546,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3589,6 +3602,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3614,12 +3628,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3636,12 +3650,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
